--- a/tests/reports/selenium_web_300_report.xlsx
+++ b/tests/reports/selenium_web_300_report.xlsx
@@ -3101,7 +3101,7 @@
         <v>35</v>
       </c>
       <c r="J2" s="6">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>36</v>
@@ -3139,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="J3" s="8">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>36</v>
@@ -3177,7 +3177,7 @@
         <v>49</v>
       </c>
       <c r="J4" s="6">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>36</v>
@@ -3215,7 +3215,7 @@
         <v>55</v>
       </c>
       <c r="J5" s="8">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>36</v>
@@ -3253,7 +3253,7 @@
         <v>35</v>
       </c>
       <c r="J6" s="6">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>36</v>
@@ -3291,7 +3291,7 @@
         <v>43</v>
       </c>
       <c r="J7" s="8">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>36</v>
@@ -3329,7 +3329,7 @@
         <v>49</v>
       </c>
       <c r="J8" s="6">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>36</v>
@@ -3367,7 +3367,7 @@
         <v>55</v>
       </c>
       <c r="J9" s="8">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>36</v>
@@ -3405,7 +3405,7 @@
         <v>35</v>
       </c>
       <c r="J10" s="6">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>36</v>
@@ -3443,7 +3443,7 @@
         <v>43</v>
       </c>
       <c r="J11" s="8">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>36</v>
@@ -3481,7 +3481,7 @@
         <v>49</v>
       </c>
       <c r="J12" s="6">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>36</v>
@@ -3519,7 +3519,7 @@
         <v>55</v>
       </c>
       <c r="J13" s="8">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>36</v>
@@ -3557,7 +3557,7 @@
         <v>35</v>
       </c>
       <c r="J14" s="6">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>36</v>
@@ -3595,7 +3595,7 @@
         <v>43</v>
       </c>
       <c r="J15" s="8">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>36</v>
@@ -3633,7 +3633,7 @@
         <v>49</v>
       </c>
       <c r="J16" s="6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>36</v>
@@ -3671,7 +3671,7 @@
         <v>55</v>
       </c>
       <c r="J17" s="8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>36</v>
@@ -3709,7 +3709,7 @@
         <v>35</v>
       </c>
       <c r="J18" s="6">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>36</v>
@@ -3747,7 +3747,7 @@
         <v>43</v>
       </c>
       <c r="J19" s="8">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>36</v>
@@ -3785,7 +3785,7 @@
         <v>49</v>
       </c>
       <c r="J20" s="6">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>36</v>
@@ -3823,7 +3823,7 @@
         <v>55</v>
       </c>
       <c r="J21" s="8">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>36</v>
@@ -3861,7 +3861,7 @@
         <v>35</v>
       </c>
       <c r="J22" s="6">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>36</v>
@@ -3899,7 +3899,7 @@
         <v>43</v>
       </c>
       <c r="J23" s="8">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>36</v>
@@ -3937,7 +3937,7 @@
         <v>49</v>
       </c>
       <c r="J24" s="6">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>36</v>
@@ -3975,7 +3975,7 @@
         <v>55</v>
       </c>
       <c r="J25" s="8">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>36</v>
@@ -4013,7 +4013,7 @@
         <v>35</v>
       </c>
       <c r="J26" s="6">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>36</v>
@@ -4051,7 +4051,7 @@
         <v>43</v>
       </c>
       <c r="J27" s="8">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>36</v>
@@ -4089,7 +4089,7 @@
         <v>49</v>
       </c>
       <c r="J28" s="6">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>36</v>
@@ -4127,7 +4127,7 @@
         <v>55</v>
       </c>
       <c r="J29" s="8">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>36</v>
@@ -4165,7 +4165,7 @@
         <v>35</v>
       </c>
       <c r="J30" s="6">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>36</v>
@@ -4203,7 +4203,7 @@
         <v>43</v>
       </c>
       <c r="J31" s="8">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>36</v>
@@ -4241,7 +4241,7 @@
         <v>49</v>
       </c>
       <c r="J32" s="6">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>36</v>
@@ -4279,7 +4279,7 @@
         <v>55</v>
       </c>
       <c r="J33" s="8">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>36</v>
@@ -4317,7 +4317,7 @@
         <v>35</v>
       </c>
       <c r="J34" s="6">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>36</v>
@@ -4355,7 +4355,7 @@
         <v>43</v>
       </c>
       <c r="J35" s="8">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>36</v>
@@ -4393,7 +4393,7 @@
         <v>49</v>
       </c>
       <c r="J36" s="6">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>36</v>
@@ -4431,7 +4431,7 @@
         <v>55</v>
       </c>
       <c r="J37" s="8">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>36</v>
@@ -4469,7 +4469,7 @@
         <v>35</v>
       </c>
       <c r="J38" s="6">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>36</v>
@@ -4507,7 +4507,7 @@
         <v>43</v>
       </c>
       <c r="J39" s="8">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>36</v>
@@ -4545,7 +4545,7 @@
         <v>49</v>
       </c>
       <c r="J40" s="6">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>36</v>
@@ -4583,7 +4583,7 @@
         <v>55</v>
       </c>
       <c r="J41" s="8">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>36</v>
@@ -4621,7 +4621,7 @@
         <v>35</v>
       </c>
       <c r="J42" s="6">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>36</v>
@@ -4697,7 +4697,7 @@
         <v>49</v>
       </c>
       <c r="J44" s="6">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="K44" s="5" t="s">
         <v>36</v>
@@ -4735,7 +4735,7 @@
         <v>55</v>
       </c>
       <c r="J45" s="8">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>36</v>
@@ -4773,7 +4773,7 @@
         <v>35</v>
       </c>
       <c r="J46" s="6">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>36</v>
@@ -4811,7 +4811,7 @@
         <v>43</v>
       </c>
       <c r="J47" s="8">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>36</v>
@@ -4849,7 +4849,7 @@
         <v>49</v>
       </c>
       <c r="J48" s="6">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="K48" s="5" t="s">
         <v>36</v>
@@ -4887,7 +4887,7 @@
         <v>55</v>
       </c>
       <c r="J49" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>36</v>
@@ -4925,7 +4925,7 @@
         <v>35</v>
       </c>
       <c r="J50" s="6">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="K50" s="5" t="s">
         <v>36</v>
@@ -4963,7 +4963,7 @@
         <v>43</v>
       </c>
       <c r="J51" s="8">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>36</v>
@@ -5001,7 +5001,7 @@
         <v>49</v>
       </c>
       <c r="J52" s="6">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="K52" s="5" t="s">
         <v>36</v>
@@ -5039,7 +5039,7 @@
         <v>55</v>
       </c>
       <c r="J53" s="8">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>36</v>
@@ -5077,7 +5077,7 @@
         <v>35</v>
       </c>
       <c r="J54" s="6">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="K54" s="5" t="s">
         <v>36</v>
@@ -5115,7 +5115,7 @@
         <v>43</v>
       </c>
       <c r="J55" s="8">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>36</v>
@@ -5153,7 +5153,7 @@
         <v>49</v>
       </c>
       <c r="J56" s="6">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K56" s="5" t="s">
         <v>36</v>
@@ -5191,7 +5191,7 @@
         <v>55</v>
       </c>
       <c r="J57" s="8">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>36</v>
@@ -5229,7 +5229,7 @@
         <v>35</v>
       </c>
       <c r="J58" s="6">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="K58" s="5" t="s">
         <v>36</v>
@@ -5267,7 +5267,7 @@
         <v>43</v>
       </c>
       <c r="J59" s="8">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>36</v>
@@ -5305,7 +5305,7 @@
         <v>49</v>
       </c>
       <c r="J60" s="6">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="K60" s="5" t="s">
         <v>36</v>
@@ -5343,7 +5343,7 @@
         <v>55</v>
       </c>
       <c r="J61" s="8">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>36</v>
@@ -5381,7 +5381,7 @@
         <v>35</v>
       </c>
       <c r="J62" s="6">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>36</v>
@@ -5419,7 +5419,7 @@
         <v>43</v>
       </c>
       <c r="J63" s="8">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="K63" s="9" t="s">
         <v>36</v>
@@ -5457,7 +5457,7 @@
         <v>49</v>
       </c>
       <c r="J64" s="6">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="K64" s="5" t="s">
         <v>36</v>
@@ -5495,7 +5495,7 @@
         <v>55</v>
       </c>
       <c r="J65" s="8">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="K65" s="9" t="s">
         <v>36</v>
@@ -5533,7 +5533,7 @@
         <v>35</v>
       </c>
       <c r="J66" s="6">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K66" s="5" t="s">
         <v>36</v>
@@ -5571,7 +5571,7 @@
         <v>43</v>
       </c>
       <c r="J67" s="8">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="K67" s="9" t="s">
         <v>36</v>
@@ -5609,7 +5609,7 @@
         <v>49</v>
       </c>
       <c r="J68" s="6">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="K68" s="5" t="s">
         <v>36</v>
@@ -5647,7 +5647,7 @@
         <v>55</v>
       </c>
       <c r="J69" s="8">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="K69" s="9" t="s">
         <v>36</v>
@@ -5685,7 +5685,7 @@
         <v>35</v>
       </c>
       <c r="J70" s="6">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="K70" s="5" t="s">
         <v>36</v>
@@ -5723,7 +5723,7 @@
         <v>43</v>
       </c>
       <c r="J71" s="8">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="K71" s="9" t="s">
         <v>36</v>
@@ -5761,7 +5761,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="6">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="K72" s="5" t="s">
         <v>36</v>
@@ -5799,7 +5799,7 @@
         <v>55</v>
       </c>
       <c r="J73" s="8">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K73" s="9" t="s">
         <v>36</v>
@@ -5837,7 +5837,7 @@
         <v>35</v>
       </c>
       <c r="J74" s="6">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="K74" s="5" t="s">
         <v>36</v>
@@ -5875,7 +5875,7 @@
         <v>43</v>
       </c>
       <c r="J75" s="8">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="K75" s="9" t="s">
         <v>36</v>
@@ -5913,7 +5913,7 @@
         <v>49</v>
       </c>
       <c r="J76" s="6">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="K76" s="5" t="s">
         <v>36</v>
@@ -5951,7 +5951,7 @@
         <v>55</v>
       </c>
       <c r="J77" s="8">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="K77" s="9" t="s">
         <v>36</v>
@@ -5989,7 +5989,7 @@
         <v>35</v>
       </c>
       <c r="J78" s="6">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="K78" s="5" t="s">
         <v>36</v>
@@ -6027,7 +6027,7 @@
         <v>43</v>
       </c>
       <c r="J79" s="8">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>36</v>
@@ -6065,7 +6065,7 @@
         <v>49</v>
       </c>
       <c r="J80" s="6">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K80" s="5" t="s">
         <v>36</v>
@@ -6103,7 +6103,7 @@
         <v>55</v>
       </c>
       <c r="J81" s="8">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="K81" s="9" t="s">
         <v>36</v>
@@ -6141,7 +6141,7 @@
         <v>35</v>
       </c>
       <c r="J82" s="6">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="K82" s="5" t="s">
         <v>36</v>
@@ -6179,7 +6179,7 @@
         <v>43</v>
       </c>
       <c r="J83" s="8">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="K83" s="9" t="s">
         <v>36</v>
@@ -6217,7 +6217,7 @@
         <v>49</v>
       </c>
       <c r="J84" s="6">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="K84" s="5" t="s">
         <v>36</v>
@@ -6255,7 +6255,7 @@
         <v>55</v>
       </c>
       <c r="J85" s="8">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="K85" s="9" t="s">
         <v>36</v>
@@ -6293,7 +6293,7 @@
         <v>35</v>
       </c>
       <c r="J86" s="6">
-        <v>115</v>
+        <v>33</v>
       </c>
       <c r="K86" s="5" t="s">
         <v>36</v>
@@ -6331,7 +6331,7 @@
         <v>43</v>
       </c>
       <c r="J87" s="8">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="K87" s="9" t="s">
         <v>36</v>
@@ -6369,7 +6369,7 @@
         <v>49</v>
       </c>
       <c r="J88" s="6">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="K88" s="5" t="s">
         <v>36</v>
@@ -6407,7 +6407,7 @@
         <v>55</v>
       </c>
       <c r="J89" s="8">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="K89" s="9" t="s">
         <v>36</v>
@@ -6445,7 +6445,7 @@
         <v>35</v>
       </c>
       <c r="J90" s="6">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="K90" s="5" t="s">
         <v>36</v>
@@ -6483,7 +6483,7 @@
         <v>43</v>
       </c>
       <c r="J91" s="8">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="K91" s="9" t="s">
         <v>36</v>
@@ -6521,7 +6521,7 @@
         <v>49</v>
       </c>
       <c r="J92" s="6">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="K92" s="5" t="s">
         <v>36</v>
@@ -6559,7 +6559,7 @@
         <v>55</v>
       </c>
       <c r="J93" s="8">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="K93" s="9" t="s">
         <v>36</v>
@@ -6597,7 +6597,7 @@
         <v>35</v>
       </c>
       <c r="J94" s="6">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="K94" s="5" t="s">
         <v>36</v>
@@ -6635,7 +6635,7 @@
         <v>43</v>
       </c>
       <c r="J95" s="8">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="K95" s="9" t="s">
         <v>36</v>
@@ -6673,7 +6673,7 @@
         <v>49</v>
       </c>
       <c r="J96" s="6">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="K96" s="5" t="s">
         <v>36</v>
@@ -6711,7 +6711,7 @@
         <v>55</v>
       </c>
       <c r="J97" s="8">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="K97" s="9" t="s">
         <v>36</v>
@@ -6749,7 +6749,7 @@
         <v>35</v>
       </c>
       <c r="J98" s="6">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K98" s="5" t="s">
         <v>36</v>
@@ -6787,7 +6787,7 @@
         <v>43</v>
       </c>
       <c r="J99" s="8">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="K99" s="9" t="s">
         <v>36</v>
@@ -6825,7 +6825,7 @@
         <v>49</v>
       </c>
       <c r="J100" s="6">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="K100" s="5" t="s">
         <v>36</v>
@@ -6863,7 +6863,7 @@
         <v>55</v>
       </c>
       <c r="J101" s="8">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="K101" s="9" t="s">
         <v>36</v>
@@ -6901,7 +6901,7 @@
         <v>35</v>
       </c>
       <c r="J102" s="6">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K102" s="5" t="s">
         <v>36</v>
@@ -6939,7 +6939,7 @@
         <v>43</v>
       </c>
       <c r="J103" s="8">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="K103" s="9" t="s">
         <v>36</v>
@@ -6977,7 +6977,7 @@
         <v>49</v>
       </c>
       <c r="J104" s="6">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="K104" s="5" t="s">
         <v>36</v>
@@ -7015,7 +7015,7 @@
         <v>55</v>
       </c>
       <c r="J105" s="8">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="K105" s="9" t="s">
         <v>36</v>
@@ -7053,7 +7053,7 @@
         <v>35</v>
       </c>
       <c r="J106" s="6">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K106" s="5" t="s">
         <v>36</v>
@@ -7091,7 +7091,7 @@
         <v>43</v>
       </c>
       <c r="J107" s="8">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="K107" s="9" t="s">
         <v>36</v>
@@ -7129,7 +7129,7 @@
         <v>49</v>
       </c>
       <c r="J108" s="6">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="K108" s="5" t="s">
         <v>36</v>
@@ -7167,7 +7167,7 @@
         <v>55</v>
       </c>
       <c r="J109" s="8">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="K109" s="9" t="s">
         <v>36</v>
@@ -7205,7 +7205,7 @@
         <v>35</v>
       </c>
       <c r="J110" s="6">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="K110" s="5" t="s">
         <v>36</v>
@@ -7243,7 +7243,7 @@
         <v>43</v>
       </c>
       <c r="J111" s="8">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="K111" s="9" t="s">
         <v>36</v>
@@ -7281,7 +7281,7 @@
         <v>49</v>
       </c>
       <c r="J112" s="6">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>36</v>
@@ -7319,7 +7319,7 @@
         <v>55</v>
       </c>
       <c r="J113" s="8">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="K113" s="9" t="s">
         <v>36</v>
@@ -7357,7 +7357,7 @@
         <v>35</v>
       </c>
       <c r="J114" s="6">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="K114" s="5" t="s">
         <v>36</v>
@@ -7395,7 +7395,7 @@
         <v>43</v>
       </c>
       <c r="J115" s="8">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="K115" s="9" t="s">
         <v>36</v>
@@ -7433,7 +7433,7 @@
         <v>49</v>
       </c>
       <c r="J116" s="6">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="K116" s="5" t="s">
         <v>36</v>
@@ -7471,7 +7471,7 @@
         <v>55</v>
       </c>
       <c r="J117" s="8">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="K117" s="9" t="s">
         <v>36</v>
@@ -7509,7 +7509,7 @@
         <v>35</v>
       </c>
       <c r="J118" s="6">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="K118" s="5" t="s">
         <v>36</v>
@@ -7547,7 +7547,7 @@
         <v>43</v>
       </c>
       <c r="J119" s="8">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="K119" s="9" t="s">
         <v>36</v>
@@ -7585,7 +7585,7 @@
         <v>49</v>
       </c>
       <c r="J120" s="6">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K120" s="5" t="s">
         <v>36</v>
@@ -7623,7 +7623,7 @@
         <v>55</v>
       </c>
       <c r="J121" s="8">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="K121" s="9" t="s">
         <v>36</v>
@@ -7661,7 +7661,7 @@
         <v>35</v>
       </c>
       <c r="J122" s="6">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="K122" s="5" t="s">
         <v>36</v>
@@ -7699,7 +7699,7 @@
         <v>43</v>
       </c>
       <c r="J123" s="8">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="K123" s="9" t="s">
         <v>36</v>
@@ -7737,7 +7737,7 @@
         <v>49</v>
       </c>
       <c r="J124" s="6">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="K124" s="5" t="s">
         <v>36</v>
@@ -7775,7 +7775,7 @@
         <v>55</v>
       </c>
       <c r="J125" s="8">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="K125" s="9" t="s">
         <v>36</v>
@@ -7813,7 +7813,7 @@
         <v>35</v>
       </c>
       <c r="J126" s="6">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="K126" s="5" t="s">
         <v>36</v>
@@ -7851,7 +7851,7 @@
         <v>43</v>
       </c>
       <c r="J127" s="8">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="K127" s="9" t="s">
         <v>36</v>
@@ -7889,7 +7889,7 @@
         <v>49</v>
       </c>
       <c r="J128" s="6">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="K128" s="5" t="s">
         <v>36</v>
@@ -7927,7 +7927,7 @@
         <v>55</v>
       </c>
       <c r="J129" s="8">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="K129" s="9" t="s">
         <v>36</v>
@@ -7965,7 +7965,7 @@
         <v>35</v>
       </c>
       <c r="J130" s="6">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="K130" s="5" t="s">
         <v>36</v>
@@ -8003,7 +8003,7 @@
         <v>43</v>
       </c>
       <c r="J131" s="8">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="K131" s="9" t="s">
         <v>36</v>
@@ -8041,7 +8041,7 @@
         <v>49</v>
       </c>
       <c r="J132" s="6">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="K132" s="5" t="s">
         <v>36</v>
@@ -8079,7 +8079,7 @@
         <v>55</v>
       </c>
       <c r="J133" s="8">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K133" s="9" t="s">
         <v>36</v>
@@ -8117,7 +8117,7 @@
         <v>35</v>
       </c>
       <c r="J134" s="6">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="K134" s="5" t="s">
         <v>36</v>
@@ -8155,7 +8155,7 @@
         <v>43</v>
       </c>
       <c r="J135" s="8">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="K135" s="9" t="s">
         <v>36</v>
@@ -8193,7 +8193,7 @@
         <v>49</v>
       </c>
       <c r="J136" s="6">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="K136" s="5" t="s">
         <v>36</v>
@@ -8231,7 +8231,7 @@
         <v>55</v>
       </c>
       <c r="J137" s="8">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="K137" s="9" t="s">
         <v>36</v>
@@ -8269,7 +8269,7 @@
         <v>35</v>
       </c>
       <c r="J138" s="6">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="K138" s="5" t="s">
         <v>36</v>
@@ -8307,7 +8307,7 @@
         <v>43</v>
       </c>
       <c r="J139" s="8">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="K139" s="9" t="s">
         <v>36</v>
@@ -8345,7 +8345,7 @@
         <v>49</v>
       </c>
       <c r="J140" s="6">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K140" s="5" t="s">
         <v>36</v>
@@ -8383,7 +8383,7 @@
         <v>55</v>
       </c>
       <c r="J141" s="8">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="K141" s="9" t="s">
         <v>36</v>
@@ -8421,7 +8421,7 @@
         <v>35</v>
       </c>
       <c r="J142" s="6">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="K142" s="5" t="s">
         <v>36</v>
@@ -8459,7 +8459,7 @@
         <v>43</v>
       </c>
       <c r="J143" s="8">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="K143" s="9" t="s">
         <v>36</v>
@@ -8497,7 +8497,7 @@
         <v>49</v>
       </c>
       <c r="J144" s="6">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="K144" s="5" t="s">
         <v>36</v>
@@ -8535,7 +8535,7 @@
         <v>55</v>
       </c>
       <c r="J145" s="8">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="K145" s="9" t="s">
         <v>36</v>
@@ -8573,7 +8573,7 @@
         <v>35</v>
       </c>
       <c r="J146" s="6">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="K146" s="5" t="s">
         <v>36</v>
@@ -8611,7 +8611,7 @@
         <v>43</v>
       </c>
       <c r="J147" s="8">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="K147" s="9" t="s">
         <v>36</v>
@@ -8649,7 +8649,7 @@
         <v>49</v>
       </c>
       <c r="J148" s="6">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="K148" s="5" t="s">
         <v>36</v>
@@ -8687,7 +8687,7 @@
         <v>55</v>
       </c>
       <c r="J149" s="8">
-        <v>147</v>
+        <v>45</v>
       </c>
       <c r="K149" s="9" t="s">
         <v>36</v>
@@ -8725,7 +8725,7 @@
         <v>35</v>
       </c>
       <c r="J150" s="6">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K150" s="5" t="s">
         <v>36</v>
@@ -8763,7 +8763,7 @@
         <v>43</v>
       </c>
       <c r="J151" s="8">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="K151" s="9" t="s">
         <v>36</v>
@@ -8801,7 +8801,7 @@
         <v>49</v>
       </c>
       <c r="J152" s="6">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="K152" s="5" t="s">
         <v>36</v>
@@ -8839,7 +8839,7 @@
         <v>55</v>
       </c>
       <c r="J153" s="8">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="K153" s="9" t="s">
         <v>36</v>
@@ -8877,7 +8877,7 @@
         <v>35</v>
       </c>
       <c r="J154" s="6">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="K154" s="5" t="s">
         <v>36</v>
@@ -8915,7 +8915,7 @@
         <v>43</v>
       </c>
       <c r="J155" s="8">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K155" s="9" t="s">
         <v>36</v>
@@ -8953,7 +8953,7 @@
         <v>49</v>
       </c>
       <c r="J156" s="6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="K156" s="5" t="s">
         <v>36</v>
@@ -8991,7 +8991,7 @@
         <v>55</v>
       </c>
       <c r="J157" s="8">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="K157" s="9" t="s">
         <v>36</v>
@@ -9029,7 +9029,7 @@
         <v>35</v>
       </c>
       <c r="J158" s="6">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K158" s="5" t="s">
         <v>36</v>
@@ -9067,7 +9067,7 @@
         <v>43</v>
       </c>
       <c r="J159" s="8">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="K159" s="9" t="s">
         <v>36</v>
@@ -9105,7 +9105,7 @@
         <v>49</v>
       </c>
       <c r="J160" s="6">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="K160" s="5" t="s">
         <v>36</v>
@@ -9143,7 +9143,7 @@
         <v>55</v>
       </c>
       <c r="J161" s="8">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="K161" s="9" t="s">
         <v>36</v>
@@ -9181,7 +9181,7 @@
         <v>35</v>
       </c>
       <c r="J162" s="6">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="K162" s="5" t="s">
         <v>36</v>
@@ -9219,7 +9219,7 @@
         <v>43</v>
       </c>
       <c r="J163" s="8">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K163" s="9" t="s">
         <v>36</v>
@@ -9257,7 +9257,7 @@
         <v>49</v>
       </c>
       <c r="J164" s="6">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="K164" s="5" t="s">
         <v>36</v>
@@ -9295,7 +9295,7 @@
         <v>55</v>
       </c>
       <c r="J165" s="8">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="K165" s="9" t="s">
         <v>36</v>
@@ -9333,7 +9333,7 @@
         <v>35</v>
       </c>
       <c r="J166" s="6">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="K166" s="5" t="s">
         <v>36</v>
@@ -9371,7 +9371,7 @@
         <v>43</v>
       </c>
       <c r="J167" s="8">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="K167" s="9" t="s">
         <v>36</v>
@@ -9409,7 +9409,7 @@
         <v>49</v>
       </c>
       <c r="J168" s="6">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="K168" s="5" t="s">
         <v>36</v>
@@ -9447,7 +9447,7 @@
         <v>55</v>
       </c>
       <c r="J169" s="8">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K169" s="9" t="s">
         <v>36</v>
@@ -9485,7 +9485,7 @@
         <v>35</v>
       </c>
       <c r="J170" s="6">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="K170" s="5" t="s">
         <v>36</v>
@@ -9523,7 +9523,7 @@
         <v>43</v>
       </c>
       <c r="J171" s="8">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="K171" s="9" t="s">
         <v>36</v>
@@ -9561,7 +9561,7 @@
         <v>49</v>
       </c>
       <c r="J172" s="6">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="K172" s="5" t="s">
         <v>36</v>
@@ -9599,7 +9599,7 @@
         <v>55</v>
       </c>
       <c r="J173" s="8">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K173" s="9" t="s">
         <v>36</v>
@@ -9637,7 +9637,7 @@
         <v>35</v>
       </c>
       <c r="J174" s="6">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="K174" s="5" t="s">
         <v>36</v>
@@ -9675,7 +9675,7 @@
         <v>43</v>
       </c>
       <c r="J175" s="8">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="K175" s="9" t="s">
         <v>36</v>
@@ -9713,7 +9713,7 @@
         <v>49</v>
       </c>
       <c r="J176" s="6">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="K176" s="5" t="s">
         <v>36</v>
@@ -9751,7 +9751,7 @@
         <v>55</v>
       </c>
       <c r="J177" s="8">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="K177" s="9" t="s">
         <v>36</v>
@@ -9789,7 +9789,7 @@
         <v>35</v>
       </c>
       <c r="J178" s="6">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="K178" s="5" t="s">
         <v>36</v>
@@ -9827,7 +9827,7 @@
         <v>43</v>
       </c>
       <c r="J179" s="8">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="K179" s="9" t="s">
         <v>36</v>
@@ -9865,7 +9865,7 @@
         <v>49</v>
       </c>
       <c r="J180" s="6">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K180" s="5" t="s">
         <v>36</v>
@@ -9903,7 +9903,7 @@
         <v>55</v>
       </c>
       <c r="J181" s="8">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="K181" s="9" t="s">
         <v>36</v>
@@ -9941,7 +9941,7 @@
         <v>35</v>
       </c>
       <c r="J182" s="6">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="K182" s="5" t="s">
         <v>36</v>
@@ -9979,7 +9979,7 @@
         <v>43</v>
       </c>
       <c r="J183" s="8">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="K183" s="9" t="s">
         <v>36</v>
@@ -10017,7 +10017,7 @@
         <v>49</v>
       </c>
       <c r="J184" s="6">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K184" s="5" t="s">
         <v>36</v>
@@ -10055,7 +10055,7 @@
         <v>55</v>
       </c>
       <c r="J185" s="8">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K185" s="9" t="s">
         <v>36</v>
@@ -10093,7 +10093,7 @@
         <v>35</v>
       </c>
       <c r="J186" s="6">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="K186" s="5" t="s">
         <v>36</v>
@@ -10131,7 +10131,7 @@
         <v>43</v>
       </c>
       <c r="J187" s="8">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K187" s="9" t="s">
         <v>36</v>
@@ -10169,7 +10169,7 @@
         <v>49</v>
       </c>
       <c r="J188" s="6">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="K188" s="5" t="s">
         <v>36</v>
@@ -10207,7 +10207,7 @@
         <v>55</v>
       </c>
       <c r="J189" s="8">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="K189" s="9" t="s">
         <v>36</v>
@@ -10245,7 +10245,7 @@
         <v>35</v>
       </c>
       <c r="J190" s="6">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="K190" s="5" t="s">
         <v>36</v>
@@ -10283,7 +10283,7 @@
         <v>43</v>
       </c>
       <c r="J191" s="8">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="K191" s="9" t="s">
         <v>36</v>
@@ -10321,7 +10321,7 @@
         <v>49</v>
       </c>
       <c r="J192" s="6">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="K192" s="5" t="s">
         <v>36</v>
@@ -10359,7 +10359,7 @@
         <v>55</v>
       </c>
       <c r="J193" s="8">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="K193" s="9" t="s">
         <v>36</v>
@@ -10397,7 +10397,7 @@
         <v>35</v>
       </c>
       <c r="J194" s="6">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="K194" s="5" t="s">
         <v>36</v>
@@ -10435,7 +10435,7 @@
         <v>43</v>
       </c>
       <c r="J195" s="8">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="K195" s="9" t="s">
         <v>36</v>
@@ -10473,7 +10473,7 @@
         <v>49</v>
       </c>
       <c r="J196" s="6">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="K196" s="5" t="s">
         <v>36</v>
@@ -10511,7 +10511,7 @@
         <v>55</v>
       </c>
       <c r="J197" s="8">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="K197" s="9" t="s">
         <v>36</v>
@@ -10549,7 +10549,7 @@
         <v>35</v>
       </c>
       <c r="J198" s="6">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="K198" s="5" t="s">
         <v>36</v>
@@ -10587,7 +10587,7 @@
         <v>43</v>
       </c>
       <c r="J199" s="8">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K199" s="9" t="s">
         <v>36</v>
@@ -10625,7 +10625,7 @@
         <v>49</v>
       </c>
       <c r="J200" s="6">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="K200" s="5" t="s">
         <v>36</v>
@@ -10663,7 +10663,7 @@
         <v>55</v>
       </c>
       <c r="J201" s="8">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="K201" s="9" t="s">
         <v>36</v>
@@ -10701,7 +10701,7 @@
         <v>35</v>
       </c>
       <c r="J202" s="6">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="K202" s="5" t="s">
         <v>36</v>
@@ -10739,7 +10739,7 @@
         <v>43</v>
       </c>
       <c r="J203" s="8">
-        <v>147</v>
+        <v>50</v>
       </c>
       <c r="K203" s="9" t="s">
         <v>36</v>
@@ -10777,7 +10777,7 @@
         <v>49</v>
       </c>
       <c r="J204" s="6">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="K204" s="5" t="s">
         <v>36</v>
@@ -10815,7 +10815,7 @@
         <v>55</v>
       </c>
       <c r="J205" s="8">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="K205" s="9" t="s">
         <v>36</v>
@@ -10853,7 +10853,7 @@
         <v>35</v>
       </c>
       <c r="J206" s="6">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="K206" s="5" t="s">
         <v>36</v>
@@ -10891,7 +10891,7 @@
         <v>43</v>
       </c>
       <c r="J207" s="8">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="K207" s="9" t="s">
         <v>36</v>
@@ -10929,7 +10929,7 @@
         <v>49</v>
       </c>
       <c r="J208" s="6">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="K208" s="5" t="s">
         <v>36</v>
@@ -10967,7 +10967,7 @@
         <v>55</v>
       </c>
       <c r="J209" s="8">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K209" s="9" t="s">
         <v>36</v>
@@ -11005,7 +11005,7 @@
         <v>35</v>
       </c>
       <c r="J210" s="6">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="K210" s="5" t="s">
         <v>36</v>
@@ -11043,7 +11043,7 @@
         <v>43</v>
       </c>
       <c r="J211" s="8">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="K211" s="9" t="s">
         <v>36</v>
@@ -11081,7 +11081,7 @@
         <v>49</v>
       </c>
       <c r="J212" s="6">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="K212" s="5" t="s">
         <v>36</v>
@@ -11119,7 +11119,7 @@
         <v>55</v>
       </c>
       <c r="J213" s="8">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K213" s="9" t="s">
         <v>36</v>
@@ -11157,7 +11157,7 @@
         <v>35</v>
       </c>
       <c r="J214" s="6">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K214" s="5" t="s">
         <v>36</v>
@@ -11195,7 +11195,7 @@
         <v>43</v>
       </c>
       <c r="J215" s="8">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="K215" s="9" t="s">
         <v>36</v>
@@ -11233,7 +11233,7 @@
         <v>49</v>
       </c>
       <c r="J216" s="6">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="K216" s="5" t="s">
         <v>36</v>
@@ -11271,7 +11271,7 @@
         <v>55</v>
       </c>
       <c r="J217" s="8">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="K217" s="9" t="s">
         <v>36</v>
@@ -11309,7 +11309,7 @@
         <v>35</v>
       </c>
       <c r="J218" s="6">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="K218" s="5" t="s">
         <v>36</v>
@@ -11347,7 +11347,7 @@
         <v>43</v>
       </c>
       <c r="J219" s="8">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="K219" s="9" t="s">
         <v>36</v>
@@ -11385,7 +11385,7 @@
         <v>49</v>
       </c>
       <c r="J220" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K220" s="5" t="s">
         <v>36</v>
@@ -11423,7 +11423,7 @@
         <v>55</v>
       </c>
       <c r="J221" s="8">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K221" s="9" t="s">
         <v>36</v>
@@ -11461,7 +11461,7 @@
         <v>35</v>
       </c>
       <c r="J222" s="6">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="K222" s="5" t="s">
         <v>36</v>
@@ -11499,7 +11499,7 @@
         <v>43</v>
       </c>
       <c r="J223" s="8">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="K223" s="9" t="s">
         <v>36</v>
@@ -11537,7 +11537,7 @@
         <v>49</v>
       </c>
       <c r="J224" s="6">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="K224" s="5" t="s">
         <v>36</v>
@@ -11575,7 +11575,7 @@
         <v>55</v>
       </c>
       <c r="J225" s="8">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="K225" s="9" t="s">
         <v>36</v>
@@ -11613,7 +11613,7 @@
         <v>35</v>
       </c>
       <c r="J226" s="6">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="K226" s="5" t="s">
         <v>36</v>
@@ -11651,7 +11651,7 @@
         <v>43</v>
       </c>
       <c r="J227" s="8">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="K227" s="9" t="s">
         <v>36</v>
@@ -11689,7 +11689,7 @@
         <v>49</v>
       </c>
       <c r="J228" s="6">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="K228" s="5" t="s">
         <v>36</v>
@@ -11727,7 +11727,7 @@
         <v>55</v>
       </c>
       <c r="J229" s="8">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="K229" s="9" t="s">
         <v>36</v>
@@ -11765,7 +11765,7 @@
         <v>35</v>
       </c>
       <c r="J230" s="6">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="K230" s="5" t="s">
         <v>36</v>
@@ -11803,7 +11803,7 @@
         <v>43</v>
       </c>
       <c r="J231" s="8">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="K231" s="9" t="s">
         <v>36</v>
@@ -11841,7 +11841,7 @@
         <v>49</v>
       </c>
       <c r="J232" s="6">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K232" s="5" t="s">
         <v>36</v>
@@ -11879,7 +11879,7 @@
         <v>55</v>
       </c>
       <c r="J233" s="8">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="K233" s="9" t="s">
         <v>36</v>
@@ -11917,7 +11917,7 @@
         <v>35</v>
       </c>
       <c r="J234" s="6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K234" s="5" t="s">
         <v>36</v>
@@ -11955,7 +11955,7 @@
         <v>43</v>
       </c>
       <c r="J235" s="8">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="K235" s="9" t="s">
         <v>36</v>
@@ -11993,7 +11993,7 @@
         <v>49</v>
       </c>
       <c r="J236" s="6">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="K236" s="5" t="s">
         <v>36</v>
@@ -12031,7 +12031,7 @@
         <v>55</v>
       </c>
       <c r="J237" s="8">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="K237" s="9" t="s">
         <v>36</v>
@@ -12069,7 +12069,7 @@
         <v>35</v>
       </c>
       <c r="J238" s="6">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="K238" s="5" t="s">
         <v>36</v>
@@ -12107,7 +12107,7 @@
         <v>43</v>
       </c>
       <c r="J239" s="8">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="K239" s="9" t="s">
         <v>36</v>
@@ -12145,7 +12145,7 @@
         <v>49</v>
       </c>
       <c r="J240" s="6">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K240" s="5" t="s">
         <v>36</v>
@@ -12183,7 +12183,7 @@
         <v>55</v>
       </c>
       <c r="J241" s="8">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="K241" s="9" t="s">
         <v>36</v>
@@ -12221,7 +12221,7 @@
         <v>35</v>
       </c>
       <c r="J242" s="6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K242" s="5" t="s">
         <v>36</v>
@@ -12259,7 +12259,7 @@
         <v>43</v>
       </c>
       <c r="J243" s="8">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K243" s="9" t="s">
         <v>36</v>
@@ -12297,7 +12297,7 @@
         <v>49</v>
       </c>
       <c r="J244" s="6">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="K244" s="5" t="s">
         <v>36</v>
@@ -12335,7 +12335,7 @@
         <v>55</v>
       </c>
       <c r="J245" s="8">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K245" s="9" t="s">
         <v>36</v>
@@ -12373,7 +12373,7 @@
         <v>35</v>
       </c>
       <c r="J246" s="6">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="K246" s="5" t="s">
         <v>36</v>
@@ -12411,7 +12411,7 @@
         <v>43</v>
       </c>
       <c r="J247" s="8">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K247" s="9" t="s">
         <v>36</v>
@@ -12449,7 +12449,7 @@
         <v>49</v>
       </c>
       <c r="J248" s="6">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="K248" s="5" t="s">
         <v>36</v>
@@ -12487,7 +12487,7 @@
         <v>55</v>
       </c>
       <c r="J249" s="8">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="K249" s="9" t="s">
         <v>36</v>
@@ -12525,7 +12525,7 @@
         <v>35</v>
       </c>
       <c r="J250" s="6">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K250" s="5" t="s">
         <v>36</v>
@@ -12563,7 +12563,7 @@
         <v>43</v>
       </c>
       <c r="J251" s="8">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="K251" s="9" t="s">
         <v>36</v>
@@ -12601,7 +12601,7 @@
         <v>49</v>
       </c>
       <c r="J252" s="6">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="K252" s="5" t="s">
         <v>36</v>
@@ -12639,7 +12639,7 @@
         <v>55</v>
       </c>
       <c r="J253" s="8">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="K253" s="9" t="s">
         <v>36</v>
@@ -12677,7 +12677,7 @@
         <v>35</v>
       </c>
       <c r="J254" s="6">
-        <v>39</v>
+        <v>141</v>
       </c>
       <c r="K254" s="5" t="s">
         <v>36</v>
@@ -12715,7 +12715,7 @@
         <v>43</v>
       </c>
       <c r="J255" s="8">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="K255" s="9" t="s">
         <v>36</v>
@@ -12753,7 +12753,7 @@
         <v>49</v>
       </c>
       <c r="J256" s="6">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="K256" s="5" t="s">
         <v>36</v>
@@ -12791,7 +12791,7 @@
         <v>55</v>
       </c>
       <c r="J257" s="8">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="K257" s="9" t="s">
         <v>36</v>
@@ -12829,7 +12829,7 @@
         <v>35</v>
       </c>
       <c r="J258" s="6">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="K258" s="5" t="s">
         <v>36</v>
@@ -12867,7 +12867,7 @@
         <v>43</v>
       </c>
       <c r="J259" s="8">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="K259" s="9" t="s">
         <v>36</v>
@@ -12905,7 +12905,7 @@
         <v>49</v>
       </c>
       <c r="J260" s="6">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="K260" s="5" t="s">
         <v>36</v>
@@ -12943,7 +12943,7 @@
         <v>55</v>
       </c>
       <c r="J261" s="8">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="K261" s="9" t="s">
         <v>36</v>
@@ -12981,7 +12981,7 @@
         <v>35</v>
       </c>
       <c r="J262" s="6">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="K262" s="5" t="s">
         <v>36</v>
@@ -13019,7 +13019,7 @@
         <v>43</v>
       </c>
       <c r="J263" s="8">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="K263" s="9" t="s">
         <v>36</v>
@@ -13095,7 +13095,7 @@
         <v>55</v>
       </c>
       <c r="J265" s="8">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="K265" s="9" t="s">
         <v>36</v>
@@ -13133,7 +13133,7 @@
         <v>35</v>
       </c>
       <c r="J266" s="6">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="K266" s="5" t="s">
         <v>36</v>
@@ -13171,7 +13171,7 @@
         <v>43</v>
       </c>
       <c r="J267" s="8">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="K267" s="9" t="s">
         <v>36</v>
@@ -13209,7 +13209,7 @@
         <v>49</v>
       </c>
       <c r="J268" s="6">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="K268" s="5" t="s">
         <v>36</v>
@@ -13247,7 +13247,7 @@
         <v>55</v>
       </c>
       <c r="J269" s="8">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="K269" s="9" t="s">
         <v>36</v>
@@ -13285,7 +13285,7 @@
         <v>35</v>
       </c>
       <c r="J270" s="6">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="K270" s="5" t="s">
         <v>36</v>
@@ -13323,7 +13323,7 @@
         <v>43</v>
       </c>
       <c r="J271" s="8">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="K271" s="9" t="s">
         <v>36</v>
@@ -13361,7 +13361,7 @@
         <v>49</v>
       </c>
       <c r="J272" s="6">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="K272" s="5" t="s">
         <v>36</v>
@@ -13399,7 +13399,7 @@
         <v>55</v>
       </c>
       <c r="J273" s="8">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="K273" s="9" t="s">
         <v>36</v>
@@ -13437,7 +13437,7 @@
         <v>35</v>
       </c>
       <c r="J274" s="6">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="K274" s="5" t="s">
         <v>36</v>
@@ -13475,7 +13475,7 @@
         <v>43</v>
       </c>
       <c r="J275" s="8">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K275" s="9" t="s">
         <v>36</v>
@@ -13513,7 +13513,7 @@
         <v>49</v>
       </c>
       <c r="J276" s="6">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="K276" s="5" t="s">
         <v>36</v>
@@ -13551,7 +13551,7 @@
         <v>55</v>
       </c>
       <c r="J277" s="8">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="K277" s="9" t="s">
         <v>36</v>
@@ -13589,7 +13589,7 @@
         <v>35</v>
       </c>
       <c r="J278" s="6">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="K278" s="5" t="s">
         <v>36</v>
@@ -13627,7 +13627,7 @@
         <v>43</v>
       </c>
       <c r="J279" s="8">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="K279" s="9" t="s">
         <v>36</v>
@@ -13665,7 +13665,7 @@
         <v>49</v>
       </c>
       <c r="J280" s="6">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="K280" s="5" t="s">
         <v>36</v>
@@ -13703,7 +13703,7 @@
         <v>55</v>
       </c>
       <c r="J281" s="8">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K281" s="9" t="s">
         <v>36</v>
@@ -13741,7 +13741,7 @@
         <v>35</v>
       </c>
       <c r="J282" s="6">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="K282" s="5" t="s">
         <v>36</v>
@@ -13779,7 +13779,7 @@
         <v>43</v>
       </c>
       <c r="J283" s="8">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K283" s="9" t="s">
         <v>36</v>
@@ -13817,7 +13817,7 @@
         <v>49</v>
       </c>
       <c r="J284" s="6">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="K284" s="5" t="s">
         <v>36</v>
@@ -13855,7 +13855,7 @@
         <v>55</v>
       </c>
       <c r="J285" s="8">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="K285" s="9" t="s">
         <v>36</v>
@@ -13893,7 +13893,7 @@
         <v>35</v>
       </c>
       <c r="J286" s="6">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="K286" s="5" t="s">
         <v>36</v>
@@ -13931,7 +13931,7 @@
         <v>43</v>
       </c>
       <c r="J287" s="8">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K287" s="9" t="s">
         <v>36</v>
@@ -13969,7 +13969,7 @@
         <v>49</v>
       </c>
       <c r="J288" s="6">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K288" s="5" t="s">
         <v>36</v>
@@ -14007,7 +14007,7 @@
         <v>55</v>
       </c>
       <c r="J289" s="8">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="K289" s="9" t="s">
         <v>36</v>
@@ -14045,7 +14045,7 @@
         <v>35</v>
       </c>
       <c r="J290" s="6">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="K290" s="5" t="s">
         <v>36</v>
@@ -14083,7 +14083,7 @@
         <v>43</v>
       </c>
       <c r="J291" s="8">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="K291" s="9" t="s">
         <v>36</v>
@@ -14121,7 +14121,7 @@
         <v>49</v>
       </c>
       <c r="J292" s="6">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="K292" s="5" t="s">
         <v>36</v>
@@ -14159,7 +14159,7 @@
         <v>55</v>
       </c>
       <c r="J293" s="8">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="K293" s="9" t="s">
         <v>36</v>
@@ -14197,7 +14197,7 @@
         <v>35</v>
       </c>
       <c r="J294" s="6">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="K294" s="5" t="s">
         <v>36</v>
@@ -14235,7 +14235,7 @@
         <v>43</v>
       </c>
       <c r="J295" s="8">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="K295" s="9" t="s">
         <v>36</v>
@@ -14273,7 +14273,7 @@
         <v>49</v>
       </c>
       <c r="J296" s="6">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="K296" s="5" t="s">
         <v>36</v>
@@ -14311,7 +14311,7 @@
         <v>55</v>
       </c>
       <c r="J297" s="8">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="K297" s="9" t="s">
         <v>36</v>
@@ -14349,7 +14349,7 @@
         <v>35</v>
       </c>
       <c r="J298" s="6">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="K298" s="5" t="s">
         <v>36</v>
@@ -14387,7 +14387,7 @@
         <v>43</v>
       </c>
       <c r="J299" s="8">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K299" s="9" t="s">
         <v>36</v>
@@ -14425,7 +14425,7 @@
         <v>49</v>
       </c>
       <c r="J300" s="6">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="K300" s="5" t="s">
         <v>36</v>
@@ -14463,7 +14463,7 @@
         <v>55</v>
       </c>
       <c r="J301" s="8">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K301" s="9" t="s">
         <v>36</v>
